--- a/artfynd/A 17513-2024 artfynd.xlsx
+++ b/artfynd/A 17513-2024 artfynd.xlsx
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651732</v>
+        <v>119651736</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499156</v>
+        <v>499236</v>
       </c>
       <c r="R7" t="n">
-        <v>7134715</v>
+        <v>7134679</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651741</v>
+        <v>119651730</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,25 +1379,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499158</v>
+        <v>499181</v>
       </c>
       <c r="R8" t="n">
-        <v>7134728</v>
+        <v>7134762</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,6 +1443,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651736</v>
+        <v>119651739</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>91832</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499236</v>
+        <v>499229</v>
       </c>
       <c r="R9" t="n">
-        <v>7134679</v>
+        <v>7134733</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,11 +1550,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651744</v>
+        <v>119651741</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,25 +1588,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499227</v>
+        <v>499158</v>
       </c>
       <c r="R10" t="n">
-        <v>7134692</v>
+        <v>7134728</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651743</v>
+        <v>119651732</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,25 +1690,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499227</v>
+        <v>499156</v>
       </c>
       <c r="R11" t="n">
-        <v>7134731</v>
+        <v>7134715</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1754,6 +1754,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651733</v>
+        <v>119651729</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>87406</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1820,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499163</v>
+        <v>499260</v>
       </c>
       <c r="R12" t="n">
-        <v>7134707</v>
+        <v>7134714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1856,11 +1861,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119651739</v>
+        <v>119651737</v>
       </c>
       <c r="B13" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,21 +1903,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499229</v>
+        <v>499235</v>
       </c>
       <c r="R13" t="n">
-        <v>7134733</v>
+        <v>7134668</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,6 +1963,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,7 +1994,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651746</v>
+        <v>119651744</v>
       </c>
       <c r="B14" t="n">
         <v>91840</v>
@@ -2029,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499280</v>
+        <v>499227</v>
       </c>
       <c r="R14" t="n">
-        <v>7134554</v>
+        <v>7134692</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2091,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119651734</v>
+        <v>119651733</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2131,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499217</v>
+        <v>499163</v>
       </c>
       <c r="R15" t="n">
-        <v>7134694</v>
+        <v>7134707</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119651729</v>
+        <v>119651734</v>
       </c>
       <c r="B16" t="n">
-        <v>87406</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,21 +2219,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2238,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499260</v>
+        <v>499217</v>
       </c>
       <c r="R16" t="n">
-        <v>7134714</v>
+        <v>7134694</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,6 +2279,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119651737</v>
+        <v>119651746</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,25 +2322,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2340,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499235</v>
+        <v>499280</v>
       </c>
       <c r="R17" t="n">
-        <v>7134668</v>
+        <v>7134554</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,11 +2386,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119651730</v>
+        <v>119651743</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2419,25 +2424,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499181</v>
+        <v>499227</v>
       </c>
       <c r="R18" t="n">
-        <v>7134762</v>
+        <v>7134731</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,11 +2488,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 17513-2024 artfynd.xlsx
+++ b/artfynd/A 17513-2024 artfynd.xlsx
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651741</v>
+        <v>119651732</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,25 +1588,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499158</v>
+        <v>499156</v>
       </c>
       <c r="R10" t="n">
-        <v>7134728</v>
+        <v>7134715</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,6 +1652,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651732</v>
+        <v>119651741</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499156</v>
+        <v>499158</v>
       </c>
       <c r="R11" t="n">
-        <v>7134715</v>
+        <v>7134728</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1754,11 +1759,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2203,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119651734</v>
+        <v>119651746</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2215,25 +2215,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499217</v>
+        <v>499280</v>
       </c>
       <c r="R16" t="n">
-        <v>7134694</v>
+        <v>7134554</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2279,11 +2279,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119651746</v>
+        <v>119651734</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2322,25 +2317,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2350,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499280</v>
+        <v>499217</v>
       </c>
       <c r="R17" t="n">
-        <v>7134554</v>
+        <v>7134694</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,6 +2381,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 17513-2024 artfynd.xlsx
+++ b/artfynd/A 17513-2024 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651736</v>
+        <v>119651729</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>87406</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499236</v>
+        <v>499260</v>
       </c>
       <c r="R7" t="n">
-        <v>7134679</v>
+        <v>7134714</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,11 +1336,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651730</v>
+        <v>119651734</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1407,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499181</v>
+        <v>499217</v>
       </c>
       <c r="R8" t="n">
-        <v>7134762</v>
+        <v>7134694</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1442,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651739</v>
+        <v>119651733</v>
       </c>
       <c r="B9" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499229</v>
+        <v>499163</v>
       </c>
       <c r="R9" t="n">
-        <v>7134733</v>
+        <v>7134707</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,6 +1545,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651741</v>
+        <v>119651730</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499158</v>
+        <v>499181</v>
       </c>
       <c r="R11" t="n">
-        <v>7134728</v>
+        <v>7134762</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,6 +1759,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651729</v>
+        <v>119651739</v>
       </c>
       <c r="B12" t="n">
-        <v>87406</v>
+        <v>91832</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4412</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499260</v>
+        <v>499229</v>
       </c>
       <c r="R12" t="n">
-        <v>7134714</v>
+        <v>7134733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119651737</v>
+        <v>119651746</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,25 +1904,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499235</v>
+        <v>499280</v>
       </c>
       <c r="R13" t="n">
-        <v>7134668</v>
+        <v>7134554</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,11 +1968,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,10 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651744</v>
+        <v>119651736</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,25 +2006,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499227</v>
+        <v>499236</v>
       </c>
       <c r="R14" t="n">
-        <v>7134692</v>
+        <v>7134679</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,6 +2070,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,7 +2101,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119651733</v>
+        <v>119651737</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2136,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499163</v>
+        <v>499235</v>
       </c>
       <c r="R15" t="n">
-        <v>7134707</v>
+        <v>7134668</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,7 +2181,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119651746</v>
+        <v>119651741</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2215,25 +2220,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2243,10 +2248,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499280</v>
+        <v>499158</v>
       </c>
       <c r="R16" t="n">
-        <v>7134554</v>
+        <v>7134728</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119651734</v>
+        <v>119651744</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,25 +2322,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499217</v>
+        <v>499227</v>
       </c>
       <c r="R17" t="n">
-        <v>7134694</v>
+        <v>7134692</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,11 +2386,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 17513-2024 artfynd.xlsx
+++ b/artfynd/A 17513-2024 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651730</v>
+        <v>119651739</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>91832</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499181</v>
+        <v>499229</v>
       </c>
       <c r="R11" t="n">
-        <v>7134762</v>
+        <v>7134733</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,11 +1759,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651739</v>
+        <v>119651730</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499229</v>
+        <v>499181</v>
       </c>
       <c r="R12" t="n">
-        <v>7134733</v>
+        <v>7134762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1866,6 +1861,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 17513-2024 artfynd.xlsx
+++ b/artfynd/A 17513-2024 artfynd.xlsx
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651734</v>
+        <v>119651741</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499217</v>
+        <v>499158</v>
       </c>
       <c r="R8" t="n">
-        <v>7134694</v>
+        <v>7134728</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,11 +1438,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651733</v>
+        <v>119651736</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1509,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499163</v>
+        <v>499236</v>
       </c>
       <c r="R9" t="n">
-        <v>7134707</v>
+        <v>7134679</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651732</v>
+        <v>119651733</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1616,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499156</v>
+        <v>499163</v>
       </c>
       <c r="R10" t="n">
-        <v>7134715</v>
+        <v>7134707</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1651,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651739</v>
+        <v>119651734</v>
       </c>
       <c r="B11" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499229</v>
+        <v>499217</v>
       </c>
       <c r="R11" t="n">
-        <v>7134733</v>
+        <v>7134694</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,6 +1754,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651730</v>
+        <v>119651737</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499181</v>
+        <v>499235</v>
       </c>
       <c r="R12" t="n">
-        <v>7134762</v>
+        <v>7134668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119651746</v>
+        <v>119651730</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,25 +1904,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499280</v>
+        <v>499181</v>
       </c>
       <c r="R13" t="n">
-        <v>7134554</v>
+        <v>7134762</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,6 +1968,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651736</v>
+        <v>119651746</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,25 +2011,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2034,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499236</v>
+        <v>499280</v>
       </c>
       <c r="R14" t="n">
-        <v>7134679</v>
+        <v>7134554</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,11 +2075,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,10 +2101,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119651737</v>
+        <v>119651744</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2113,25 +2113,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499235</v>
+        <v>499227</v>
       </c>
       <c r="R15" t="n">
-        <v>7134668</v>
+        <v>7134692</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2177,11 +2177,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119651741</v>
+        <v>119651743</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2220,25 +2215,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2248,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499158</v>
+        <v>499227</v>
       </c>
       <c r="R16" t="n">
-        <v>7134728</v>
+        <v>7134731</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2310,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119651744</v>
+        <v>119651739</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2322,25 +2317,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2350,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499227</v>
+        <v>499229</v>
       </c>
       <c r="R17" t="n">
-        <v>7134692</v>
+        <v>7134733</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2412,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119651743</v>
+        <v>119651732</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2424,25 +2419,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2452,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499227</v>
+        <v>499156</v>
       </c>
       <c r="R18" t="n">
-        <v>7134731</v>
+        <v>7134715</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,6 +2483,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 17513-2024 artfynd.xlsx
+++ b/artfynd/A 17513-2024 artfynd.xlsx
@@ -2305,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119651739</v>
+        <v>119651732</v>
       </c>
       <c r="B17" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499229</v>
+        <v>499156</v>
       </c>
       <c r="R17" t="n">
-        <v>7134733</v>
+        <v>7134715</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,6 +2381,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119651732</v>
+        <v>119651739</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>91832</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2428,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499156</v>
+        <v>499229</v>
       </c>
       <c r="R18" t="n">
-        <v>7134715</v>
+        <v>7134733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,11 +2488,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 17513-2024 artfynd.xlsx
+++ b/artfynd/A 17513-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100082797</v>
+        <v>100082799</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499225.4909603678</v>
+        <v>499254</v>
       </c>
       <c r="R2" t="n">
-        <v>7134795.453899165</v>
+        <v>7134693</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2021-10-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100082800</v>
+        <v>119651739</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ström-Alanäs, Jmt</t>
+          <t>Torsfjärden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499231.1037073407</v>
+        <v>499229</v>
       </c>
       <c r="R3" t="n">
-        <v>7134675.802529585</v>
+        <v>7134733</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,36 +858,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Susanne Wiik</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100082799</v>
+        <v>119651740</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +885,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ström-Alanäs, Jmt</t>
+          <t>Torsfjärden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499253.6795967096</v>
+        <v>499276</v>
       </c>
       <c r="R4" t="n">
-        <v>7134693.137822973</v>
+        <v>7134847</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,58 +955,48 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Susanne Wiik</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100082798</v>
+        <v>100101306</v>
       </c>
       <c r="B5" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499213.7691779156</v>
+        <v>499226</v>
       </c>
       <c r="R5" t="n">
-        <v>7134786.353239557</v>
+        <v>7134738</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,19 +1039,9 @@
           <t>2021-10-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,19 +1073,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100101306</v>
+        <v>119651743</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1179,17 +1104,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ström-Alanäs, Jmt</t>
+          <t>Torsfjärden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499226.3445449378</v>
+        <v>499227</v>
       </c>
       <c r="R6" t="n">
-        <v>7134737.796856455</v>
+        <v>7134731</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,22 +1138,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,36 +1154,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Susanne Wiik</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651729</v>
+        <v>119651744</v>
       </c>
       <c r="B7" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499260</v>
+        <v>499227</v>
       </c>
       <c r="R7" t="n">
-        <v>7134714</v>
+        <v>7134692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1362,37 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651741</v>
+        <v>119651746</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499158</v>
+        <v>499280</v>
       </c>
       <c r="R8" t="n">
-        <v>7134728</v>
+        <v>7134554</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,15 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651736</v>
+        <v>119651729</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499236</v>
+        <v>499260</v>
       </c>
       <c r="R9" t="n">
-        <v>7134679</v>
+        <v>7134714</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651733</v>
+        <v>100082800</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,37 +1472,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Torsfjärden, Jmt</t>
+          <t>Ström-Alanäs, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499163</v>
+        <v>499231</v>
       </c>
       <c r="R10" t="n">
-        <v>7134707</v>
+        <v>7134676</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,17 +1526,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2021-10-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2021-10-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,69 +1542,69 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Susanne Wiik</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651734</v>
+        <v>100082797</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Torsfjärden, Jmt</t>
+          <t>Ström-Alanäs, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499217</v>
+        <v>499225</v>
       </c>
       <c r="R11" t="n">
-        <v>7134694</v>
+        <v>7134795</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,17 +1628,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2021-10-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2021-10-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,69 +1644,69 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Susanne Wiik</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651737</v>
+        <v>100082798</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Torsfjärden, Jmt</t>
+          <t>Ström-Alanäs, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499235</v>
+        <v>499214</v>
       </c>
       <c r="R12" t="n">
-        <v>7134668</v>
+        <v>7134786</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,17 +1730,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2021-10-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2021-10-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,16 +1746,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Susanne Wiik</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1895,12 +1770,7 @@
         <v>119651730</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,37 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651746</v>
+        <v>119651731</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2039,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499280</v>
+        <v>499169</v>
       </c>
       <c r="R14" t="n">
-        <v>7134554</v>
+        <v>7134764</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2075,6 +1940,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,37 +1971,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119651744</v>
+        <v>119651732</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2141,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499227</v>
+        <v>499156</v>
       </c>
       <c r="R15" t="n">
-        <v>7134692</v>
+        <v>7134715</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2177,6 +2042,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,37 +2073,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119651743</v>
+        <v>119651733</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2243,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499227</v>
+        <v>499163</v>
       </c>
       <c r="R16" t="n">
-        <v>7134731</v>
+        <v>7134707</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2279,6 +2144,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,15 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119651732</v>
+        <v>119651734</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499156</v>
+        <v>499217</v>
       </c>
       <c r="R17" t="n">
-        <v>7134715</v>
+        <v>7134694</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2385,7 +2250,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,15 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119651739</v>
+        <v>119651736</v>
       </c>
       <c r="B18" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2452,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499229</v>
+        <v>499236</v>
       </c>
       <c r="R18" t="n">
-        <v>7134733</v>
+        <v>7134679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2490,6 +2350,11 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2511,6 +2376,205 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>119651737</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Torsfjärden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>499235</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7134668</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>119651741</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Torsfjärden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>499158</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7134728</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17513-2024 artfynd.xlsx
+++ b/artfynd/A 17513-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100082799</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651739</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651740</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100101306</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651743</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651744</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651746</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651729</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100082800</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100082797</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100082798</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651730</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651731</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651732</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651733</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2274,6 +2354,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651734</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2376,6 +2461,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651736</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2478,6 +2568,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651737</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2575,8 +2670,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651741</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>